--- a/design/tables/Collection.xlsx
+++ b/design/tables/Collection.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R47af530b3fa14e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R6732d09370014f24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -425,470 +425,470 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="2" t="str">
-        <x:v>enemy-normal</x:v>
+        <x:v>staff-mint</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
-        <x:v>enemies</x:v>
+        <x:v>staff</x:v>
       </x:c>
       <x:c r="D6" s="2" t="str">
-        <x:v>normal</x:v>
+        <x:v>mint</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>enemy_normal</x:v>
+        <x:v>mint</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>collection.enemy-normal.category</x:v>
+        <x:v>collection.staff-mint.category</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>collection.enemy-normal.traits</x:v>
+        <x:v>collection.staff-mint.traits</x:v>
       </x:c>
       <x:c r="H6" s="8" t="str">
-        <x:v>collection.enemy-normal.story</x:v>
+        <x:v>collection.staff-mint.story</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
-        <x:v>enemy-swift</x:v>
+        <x:v>staff-mianmian</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>enemies</x:v>
+        <x:v>staff</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
-        <x:v>swift</x:v>
+        <x:v>frost</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>enemy_swift</x:v>
+        <x:v>frost</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>collection.enemy-swift.category</x:v>
+        <x:v>collection.staff-mianmian.category</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
-        <x:v>collection.enemy-swift.traits</x:v>
+        <x:v>collection.staff-mianmian.traits</x:v>
       </x:c>
       <x:c r="H7" s="8" t="str">
-        <x:v>collection.enemy-swift.story</x:v>
+        <x:v>collection.staff-mianmian.story</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="2" t="str">
-        <x:v>enemy-tank</x:v>
+        <x:v>staff-buding</x:v>
       </x:c>
       <x:c r="C8" s="2" t="str">
-        <x:v>enemies</x:v>
+        <x:v>staff</x:v>
       </x:c>
       <x:c r="D8" s="2" t="str">
-        <x:v>tank</x:v>
+        <x:v>bloom</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>enemy_tank</x:v>
+        <x:v>bloom</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>collection.enemy-tank.category</x:v>
+        <x:v>collection.staff-buding.category</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
-        <x:v>collection.enemy-tank.traits</x:v>
+        <x:v>collection.staff-buding.traits</x:v>
       </x:c>
       <x:c r="H8" s="8" t="str">
-        <x:v>collection.enemy-tank.story</x:v>
+        <x:v>collection.staff-buding.story</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>staff-doubao</x:v>
+        <x:v>staff-ember</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
         <x:v>staff</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>sprout</x:v>
+        <x:v>ember</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>sprout</x:v>
+        <x:v>ember</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>collection.staff-doubao.category</x:v>
+        <x:v>collection.staff-ember.category</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
-        <x:v>collection.staff-doubao.traits</x:v>
+        <x:v>collection.staff-ember.traits</x:v>
       </x:c>
       <x:c r="H9" s="8" t="str">
-        <x:v>collection.staff-doubao.story</x:v>
+        <x:v>collection.staff-ember.story</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="2" t="str">
-        <x:v>staff-mianmian</x:v>
+        <x:v>staff-doubao</x:v>
       </x:c>
       <x:c r="C10" s="2" t="str">
         <x:v>staff</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
-        <x:v>frost</x:v>
+        <x:v>sprout</x:v>
       </x:c>
       <x:c r="E10" s="2" t="str">
-        <x:v>frost</x:v>
+        <x:v>sprout</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>collection.staff-mianmian.category</x:v>
+        <x:v>collection.staff-doubao.category</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
-        <x:v>collection.staff-mianmian.traits</x:v>
+        <x:v>collection.staff-doubao.traits</x:v>
       </x:c>
       <x:c r="H10" s="8" t="str">
-        <x:v>collection.staff-mianmian.story</x:v>
+        <x:v>collection.staff-doubao.story</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="2" t="str">
-        <x:v>staff-buding</x:v>
+        <x:v>staff-scope</x:v>
       </x:c>
       <x:c r="C11" s="2" t="str">
         <x:v>staff</x:v>
       </x:c>
       <x:c r="D11" s="2" t="str">
-        <x:v>bloom</x:v>
+        <x:v>scope</x:v>
       </x:c>
       <x:c r="E11" s="2" t="str">
-        <x:v>bloom</x:v>
+        <x:v>scope</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>collection.staff-buding.category</x:v>
+        <x:v>collection.staff-scope.category</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
-        <x:v>collection.staff-buding.traits</x:v>
+        <x:v>collection.staff-scope.traits</x:v>
       </x:c>
       <x:c r="H11" s="8" t="str">
-        <x:v>collection.staff-buding.story</x:v>
+        <x:v>collection.staff-scope.story</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="2" t="str">
-        <x:v>enemy-shield</x:v>
+        <x:v>staff-spark</x:v>
       </x:c>
       <x:c r="C12" s="2" t="str">
-        <x:v>enemies</x:v>
+        <x:v>staff</x:v>
       </x:c>
       <x:c r="D12" s="2" t="str">
-        <x:v>shield</x:v>
+        <x:v>spark</x:v>
       </x:c>
       <x:c r="E12" s="2" t="str">
-        <x:v>enemy_shield</x:v>
+        <x:v>spark</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>collection.enemy-shield.category</x:v>
+        <x:v>collection.staff-spark.category</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>collection.enemy-shield.traits</x:v>
+        <x:v>collection.staff-spark.traits</x:v>
       </x:c>
       <x:c r="H12" s="8" t="str">
-        <x:v>collection.enemy-shield.story</x:v>
+        <x:v>collection.staff-spark.story</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="2" t="str">
-        <x:v>enemy-jelly</x:v>
+        <x:v>staff-fan</x:v>
       </x:c>
       <x:c r="C13" s="2" t="str">
-        <x:v>enemies</x:v>
+        <x:v>staff</x:v>
       </x:c>
       <x:c r="D13" s="2" t="str">
-        <x:v>jelly</x:v>
+        <x:v>fan</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>enemy_jelly</x:v>
+        <x:v>fan</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>collection.enemy-jelly.category</x:v>
+        <x:v>collection.staff-fan.category</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
-        <x:v>collection.enemy-jelly.traits</x:v>
+        <x:v>collection.staff-fan.traits</x:v>
       </x:c>
       <x:c r="H13" s="8" t="str">
-        <x:v>collection.enemy-jelly.story</x:v>
+        <x:v>collection.staff-fan.story</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="2" t="str">
-        <x:v>enemy-runner</x:v>
+        <x:v>enemy-normal</x:v>
       </x:c>
       <x:c r="C14" s="2" t="str">
         <x:v>enemies</x:v>
       </x:c>
       <x:c r="D14" s="2" t="str">
-        <x:v>runner</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E14" s="2" t="str">
-        <x:v>enemy_runner</x:v>
+        <x:v>enemy_normal</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>collection.enemy-runner.category</x:v>
+        <x:v>collection.enemy-normal.category</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
-        <x:v>collection.enemy-runner.traits</x:v>
+        <x:v>collection.enemy-normal.traits</x:v>
       </x:c>
       <x:c r="H14" s="8" t="str">
-        <x:v>collection.enemy-runner.story</x:v>
+        <x:v>collection.enemy-normal.story</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
-        <x:v>boss-postmaster</x:v>
+        <x:v>enemy-swift</x:v>
       </x:c>
       <x:c r="C15" s="2" t="str">
-        <x:v>bosses</x:v>
+        <x:v>enemies</x:v>
       </x:c>
       <x:c r="D15" s="2" t="str">
-        <x:v>postmaster</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E15" s="2" t="str">
-        <x:v>enemy_postmaster</x:v>
+        <x:v>enemy_swift</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>collection.boss-postmaster.category</x:v>
+        <x:v>collection.enemy-swift.category</x:v>
       </x:c>
       <x:c r="G15" s="8" t="str">
-        <x:v>collection.boss-postmaster.traits</x:v>
+        <x:v>collection.enemy-swift.traits</x:v>
       </x:c>
       <x:c r="H15" s="8" t="str">
-        <x:v>collection.boss-postmaster.story</x:v>
+        <x:v>collection.enemy-swift.story</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="2" t="str">
-        <x:v>boss-fog-guest</x:v>
+        <x:v>enemy-shield</x:v>
       </x:c>
       <x:c r="C16" s="2" t="str">
-        <x:v>bosses</x:v>
+        <x:v>enemies</x:v>
       </x:c>
       <x:c r="D16" s="2" t="str">
-        <x:v>lantern</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E16" s="2" t="str">
-        <x:v>enemy_lantern</x:v>
+        <x:v>enemy_shield</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>collection.boss-fog-guest.category</x:v>
+        <x:v>collection.enemy-shield.category</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
-        <x:v>collection.boss-fog-guest.traits</x:v>
+        <x:v>collection.enemy-shield.traits</x:v>
       </x:c>
       <x:c r="H16" s="8" t="str">
-        <x:v>collection.boss-fog-guest.story</x:v>
+        <x:v>collection.enemy-shield.story</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A17" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>boss-midnight-leader</x:v>
+        <x:v>enemy-jelly</x:v>
       </x:c>
       <x:c r="C17" s="2" t="str">
-        <x:v>bosses</x:v>
+        <x:v>enemies</x:v>
       </x:c>
       <x:c r="D17" s="2" t="str">
-        <x:v>chef</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E17" s="2" t="str">
-        <x:v>enemy_chef</x:v>
+        <x:v>enemy_jelly</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>collection.boss-midnight-leader.category</x:v>
+        <x:v>collection.enemy-jelly.category</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
-        <x:v>collection.boss-midnight-leader.traits</x:v>
+        <x:v>collection.enemy-jelly.traits</x:v>
       </x:c>
       <x:c r="H17" s="8" t="str">
-        <x:v>collection.boss-midnight-leader.story</x:v>
+        <x:v>collection.enemy-jelly.story</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B18" s="2" t="str">
-        <x:v>boss-clock</x:v>
+        <x:v>enemy-runner</x:v>
       </x:c>
       <x:c r="C18" s="2" t="str">
-        <x:v>bosses</x:v>
+        <x:v>enemies</x:v>
       </x:c>
       <x:c r="D18" s="2" t="str">
-        <x:v>clock</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E18" s="2" t="str">
-        <x:v>enemy_clock</x:v>
+        <x:v>enemy_runner</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>collection.boss-clock.category</x:v>
+        <x:v>collection.enemy-runner.category</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
-        <x:v>collection.boss-clock.traits</x:v>
+        <x:v>collection.enemy-runner.traits</x:v>
       </x:c>
       <x:c r="H18" s="8" t="str">
-        <x:v>collection.boss-clock.story</x:v>
+        <x:v>collection.enemy-runner.story</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
-        <x:v>staff-scope</x:v>
+        <x:v>enemy-tank</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>staff</x:v>
+        <x:v>enemies</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
-        <x:v>scope</x:v>
+        <x:v>tank</x:v>
       </x:c>
       <x:c r="E19" s="2" t="str">
-        <x:v>scope</x:v>
+        <x:v>enemy_tank</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>collection.staff-scope.category</x:v>
+        <x:v>collection.enemy-tank.category</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
-        <x:v>collection.staff-scope.traits</x:v>
+        <x:v>collection.enemy-tank.traits</x:v>
       </x:c>
       <x:c r="H19" s="8" t="str">
-        <x:v>collection.staff-scope.story</x:v>
+        <x:v>collection.enemy-tank.story</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="2" t="str">
-        <x:v>staff-spark</x:v>
+        <x:v>boss-postmaster</x:v>
       </x:c>
       <x:c r="C20" s="2" t="str">
-        <x:v>staff</x:v>
+        <x:v>bosses</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:v>spark</x:v>
+        <x:v>postmaster</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:v>spark</x:v>
+        <x:v>enemy_postmaster</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>collection.staff-spark.category</x:v>
+        <x:v>collection.boss-postmaster.category</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
-        <x:v>collection.staff-spark.traits</x:v>
+        <x:v>collection.boss-postmaster.traits</x:v>
       </x:c>
       <x:c r="H20" s="8" t="str">
-        <x:v>collection.staff-spark.story</x:v>
+        <x:v>collection.boss-postmaster.story</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="2" t="str">
-        <x:v>staff-ember</x:v>
+        <x:v>boss-fog-guest</x:v>
       </x:c>
       <x:c r="C21" s="2" t="str">
-        <x:v>staff</x:v>
+        <x:v>bosses</x:v>
       </x:c>
       <x:c r="D21" s="2" t="str">
-        <x:v>ember</x:v>
+        <x:v>lantern</x:v>
       </x:c>
       <x:c r="E21" s="2" t="str">
-        <x:v>ember</x:v>
+        <x:v>enemy_lantern</x:v>
       </x:c>
       <x:c r="F21" s="8" t="str">
-        <x:v>collection.staff-ember.category</x:v>
+        <x:v>collection.boss-fog-guest.category</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
-        <x:v>collection.staff-ember.traits</x:v>
+        <x:v>collection.boss-fog-guest.traits</x:v>
       </x:c>
       <x:c r="H21" s="8" t="str">
-        <x:v>collection.staff-ember.story</x:v>
+        <x:v>collection.boss-fog-guest.story</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B22" s="2" t="str">
-        <x:v>staff-mint</x:v>
+        <x:v>boss-midnight-leader</x:v>
       </x:c>
       <x:c r="C22" s="2" t="str">
-        <x:v>staff</x:v>
+        <x:v>bosses</x:v>
       </x:c>
       <x:c r="D22" s="2" t="str">
-        <x:v>mint</x:v>
+        <x:v>chef</x:v>
       </x:c>
       <x:c r="E22" s="2" t="str">
-        <x:v>mint</x:v>
+        <x:v>enemy_chef</x:v>
       </x:c>
       <x:c r="F22" s="8" t="str">
-        <x:v>collection.staff-mint.category</x:v>
+        <x:v>collection.boss-midnight-leader.category</x:v>
       </x:c>
       <x:c r="G22" s="8" t="str">
-        <x:v>collection.staff-mint.traits</x:v>
+        <x:v>collection.boss-midnight-leader.traits</x:v>
       </x:c>
       <x:c r="H22" s="8" t="str">
-        <x:v>collection.staff-mint.story</x:v>
+        <x:v>collection.boss-midnight-leader.story</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="2" t="str">
-        <x:v>staff-fan</x:v>
+        <x:v>boss-clock</x:v>
       </x:c>
       <x:c r="C23" s="2" t="str">
-        <x:v>staff</x:v>
+        <x:v>bosses</x:v>
       </x:c>
       <x:c r="D23" s="2" t="str">
-        <x:v>fan</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E23" s="2" t="str">
-        <x:v>fan</x:v>
+        <x:v>enemy_clock</x:v>
       </x:c>
       <x:c r="F23" s="8" t="str">
-        <x:v>collection.staff-fan.category</x:v>
+        <x:v>collection.boss-clock.category</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
-        <x:v>collection.staff-fan.traits</x:v>
+        <x:v>collection.boss-clock.traits</x:v>
       </x:c>
       <x:c r="H23" s="8" t="str">
-        <x:v>collection.staff-fan.story</x:v>
+        <x:v>collection.boss-clock.story</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Collection.xlsx
+++ b/design/tables/Collection.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R6732d09370014f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R6546f2f20344434b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -891,6 +891,370 @@
         <x:v>collection.boss-clock.story</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="str">
+        <x:v>enemy-puff</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="str">
+        <x:v>puff</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="str">
+        <x:v>enemy_puff</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str">
+        <x:v>collection.enemy-puff.category</x:v>
+      </x:c>
+      <x:c r="G24" s="8" t="str">
+        <x:v>collection.enemy-puff.traits</x:v>
+      </x:c>
+      <x:c r="H24" s="8" t="str">
+        <x:v>collection.enemy-puff.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>enemy-pudding</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="str">
+        <x:v>pudding</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="str">
+        <x:v>enemy_pudding</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="str">
+        <x:v>collection.enemy-pudding.category</x:v>
+      </x:c>
+      <x:c r="G25" s="8" t="str">
+        <x:v>collection.enemy-pudding.traits</x:v>
+      </x:c>
+      <x:c r="H25" s="8" t="str">
+        <x:v>collection.enemy-pudding.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="str">
+        <x:v>enemy-biscuit</x:v>
+      </x:c>
+      <x:c r="C26" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="str">
+        <x:v>biscuit</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="str">
+        <x:v>enemy_biscuit</x:v>
+      </x:c>
+      <x:c r="F26" s="8" t="str">
+        <x:v>collection.enemy-biscuit.category</x:v>
+      </x:c>
+      <x:c r="G26" s="8" t="str">
+        <x:v>collection.enemy-biscuit.traits</x:v>
+      </x:c>
+      <x:c r="H26" s="8" t="str">
+        <x:v>collection.enemy-biscuit.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>enemy-soda</x:v>
+      </x:c>
+      <x:c r="C27" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="str">
+        <x:v>soda</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="str">
+        <x:v>enemy_soda</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="str">
+        <x:v>collection.enemy-soda.category</x:v>
+      </x:c>
+      <x:c r="G27" s="8" t="str">
+        <x:v>collection.enemy-soda.traits</x:v>
+      </x:c>
+      <x:c r="H27" s="8" t="str">
+        <x:v>collection.enemy-soda.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="str">
+        <x:v>enemy-coffee</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="str">
+        <x:v>coffee</x:v>
+      </x:c>
+      <x:c r="E28" s="2" t="str">
+        <x:v>enemy_coffee</x:v>
+      </x:c>
+      <x:c r="F28" s="8" t="str">
+        <x:v>collection.enemy-coffee.category</x:v>
+      </x:c>
+      <x:c r="G28" s="8" t="str">
+        <x:v>collection.enemy-coffee.traits</x:v>
+      </x:c>
+      <x:c r="H28" s="8" t="str">
+        <x:v>collection.enemy-coffee.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>enemy-tea</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="str">
+        <x:v>tea</x:v>
+      </x:c>
+      <x:c r="E29" s="2" t="str">
+        <x:v>enemy_tea</x:v>
+      </x:c>
+      <x:c r="F29" s="8" t="str">
+        <x:v>collection.enemy-tea.category</x:v>
+      </x:c>
+      <x:c r="G29" s="8" t="str">
+        <x:v>collection.enemy-tea.traits</x:v>
+      </x:c>
+      <x:c r="H29" s="8" t="str">
+        <x:v>collection.enemy-tea.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="str">
+        <x:v>enemy-berrymilk</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="str">
+        <x:v>berrymilk</x:v>
+      </x:c>
+      <x:c r="E30" s="2" t="str">
+        <x:v>enemy_berrymilk</x:v>
+      </x:c>
+      <x:c r="F30" s="8" t="str">
+        <x:v>collection.enemy-berrymilk.category</x:v>
+      </x:c>
+      <x:c r="G30" s="8" t="str">
+        <x:v>collection.enemy-berrymilk.traits</x:v>
+      </x:c>
+      <x:c r="H30" s="8" t="str">
+        <x:v>collection.enemy-berrymilk.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
+        <x:v>enemy-tin</x:v>
+      </x:c>
+      <x:c r="C31" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="str">
+        <x:v>tin</x:v>
+      </x:c>
+      <x:c r="E31" s="2" t="str">
+        <x:v>enemy_tin</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="str">
+        <x:v>collection.enemy-tin.category</x:v>
+      </x:c>
+      <x:c r="G31" s="8" t="str">
+        <x:v>collection.enemy-tin.traits</x:v>
+      </x:c>
+      <x:c r="H31" s="8" t="str">
+        <x:v>collection.enemy-tin.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="str">
+        <x:v>enemy-juice</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="str">
+        <x:v>juice</x:v>
+      </x:c>
+      <x:c r="E32" s="2" t="str">
+        <x:v>enemy_juice</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="str">
+        <x:v>collection.enemy-juice.category</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="str">
+        <x:v>collection.enemy-juice.traits</x:v>
+      </x:c>
+      <x:c r="H32" s="8" t="str">
+        <x:v>collection.enemy-juice.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" s="2" t="str">
+        <x:v>enemy-peach</x:v>
+      </x:c>
+      <x:c r="C33" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="str">
+        <x:v>peach</x:v>
+      </x:c>
+      <x:c r="E33" s="2" t="str">
+        <x:v>enemy_peach</x:v>
+      </x:c>
+      <x:c r="F33" s="8" t="str">
+        <x:v>collection.enemy-peach.category</x:v>
+      </x:c>
+      <x:c r="G33" s="8" t="str">
+        <x:v>collection.enemy-peach.traits</x:v>
+      </x:c>
+      <x:c r="H33" s="8" t="str">
+        <x:v>collection.enemy-peach.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="str">
+        <x:v>enemy-grape</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="str">
+        <x:v>grape</x:v>
+      </x:c>
+      <x:c r="E34" s="2" t="str">
+        <x:v>enemy_grape</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>collection.enemy-grape.category</x:v>
+      </x:c>
+      <x:c r="G34" s="8" t="str">
+        <x:v>collection.enemy-grape.traits</x:v>
+      </x:c>
+      <x:c r="H34" s="8" t="str">
+        <x:v>collection.enemy-grape.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="str">
+        <x:v>enemy-blue</x:v>
+      </x:c>
+      <x:c r="C35" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="str">
+        <x:v>blue</x:v>
+      </x:c>
+      <x:c r="E35" s="2" t="str">
+        <x:v>enemy_blue</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>collection.enemy-blue.category</x:v>
+      </x:c>
+      <x:c r="G35" s="8" t="str">
+        <x:v>collection.enemy-blue.traits</x:v>
+      </x:c>
+      <x:c r="H35" s="8" t="str">
+        <x:v>collection.enemy-blue.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="str">
+        <x:v>enemy-ricebox</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="str">
+        <x:v>ricebox</x:v>
+      </x:c>
+      <x:c r="E36" s="2" t="str">
+        <x:v>enemy_ricebox</x:v>
+      </x:c>
+      <x:c r="F36" s="8" t="str">
+        <x:v>collection.enemy-ricebox.category</x:v>
+      </x:c>
+      <x:c r="G36" s="8" t="str">
+        <x:v>collection.enemy-ricebox.traits</x:v>
+      </x:c>
+      <x:c r="H36" s="8" t="str">
+        <x:v>collection.enemy-ricebox.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="7" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="str">
+        <x:v>enemy-deliverybag</x:v>
+      </x:c>
+      <x:c r="C37" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="str">
+        <x:v>deliverybag</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="str">
+        <x:v>enemy_deliverybag</x:v>
+      </x:c>
+      <x:c r="F37" s="8" t="str">
+        <x:v>collection.enemy-deliverybag.category</x:v>
+      </x:c>
+      <x:c r="G37" s="8" t="str">
+        <x:v>collection.enemy-deliverybag.traits</x:v>
+      </x:c>
+      <x:c r="H37" s="8" t="str">
+        <x:v>collection.enemy-deliverybag.story</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Collection.xlsx
+++ b/design/tables/Collection.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R6546f2f20344434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection" sheetId="1" r:id="R670f7dad8e5f45c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1255,6 +1255,162 @@
         <x:v>collection.enemy-deliverybag.story</x:v>
       </x:c>
     </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="7" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="str">
+        <x:v>enemy-mochi</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="str">
+        <x:v>mochi</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="str">
+        <x:v>enemy_mochi</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="str">
+        <x:v>collection.enemy-mochi.category</x:v>
+      </x:c>
+      <x:c r="G38" s="8" t="str">
+        <x:v>collection.enemy-mochi.traits</x:v>
+      </x:c>
+      <x:c r="H38" s="8" t="str">
+        <x:v>collection.enemy-mochi.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="7" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="str">
+        <x:v>enemy-popcorn</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="str">
+        <x:v>popcorn</x:v>
+      </x:c>
+      <x:c r="E39" s="2" t="str">
+        <x:v>enemy_popcorn</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="str">
+        <x:v>collection.enemy-popcorn.category</x:v>
+      </x:c>
+      <x:c r="G39" s="8" t="str">
+        <x:v>collection.enemy-popcorn.traits</x:v>
+      </x:c>
+      <x:c r="H39" s="8" t="str">
+        <x:v>collection.enemy-popcorn.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="7" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="str">
+        <x:v>enemy-noodlecup</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="str">
+        <x:v>noodlecup</x:v>
+      </x:c>
+      <x:c r="E40" s="2" t="str">
+        <x:v>enemy_noodlecup</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
+        <x:v>collection.enemy-noodlecup.category</x:v>
+      </x:c>
+      <x:c r="G40" s="8" t="str">
+        <x:v>collection.enemy-noodlecup.traits</x:v>
+      </x:c>
+      <x:c r="H40" s="8" t="str">
+        <x:v>collection.enemy-noodlecup.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="7" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" s="2" t="str">
+        <x:v>enemy-frostdonut</x:v>
+      </x:c>
+      <x:c r="C41" s="2" t="str">
+        <x:v>enemies</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="str">
+        <x:v>frostdonut</x:v>
+      </x:c>
+      <x:c r="E41" s="2" t="str">
+        <x:v>enemy_frostdonut</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="str">
+        <x:v>collection.enemy-frostdonut.category</x:v>
+      </x:c>
+      <x:c r="G41" s="8" t="str">
+        <x:v>collection.enemy-frostdonut.traits</x:v>
+      </x:c>
+      <x:c r="H41" s="8" t="str">
+        <x:v>collection.enemy-frostdonut.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="str">
+        <x:v>boss-freezer</x:v>
+      </x:c>
+      <x:c r="C42" s="2" t="str">
+        <x:v>bosses</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="str">
+        <x:v>freezer</x:v>
+      </x:c>
+      <x:c r="E42" s="2" t="str">
+        <x:v>enemy_freezer</x:v>
+      </x:c>
+      <x:c r="F42" s="8" t="str">
+        <x:v>collection.boss-freezer.category</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="str">
+        <x:v>collection.boss-freezer.traits</x:v>
+      </x:c>
+      <x:c r="H42" s="8" t="str">
+        <x:v>collection.boss-freezer.story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" s="2" t="str">
+        <x:v>boss-vending</x:v>
+      </x:c>
+      <x:c r="C43" s="2" t="str">
+        <x:v>bosses</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="str">
+        <x:v>vending</x:v>
+      </x:c>
+      <x:c r="E43" s="2" t="str">
+        <x:v>enemy_vending</x:v>
+      </x:c>
+      <x:c r="F43" s="8" t="str">
+        <x:v>collection.boss-vending.category</x:v>
+      </x:c>
+      <x:c r="G43" s="8" t="str">
+        <x:v>collection.boss-vending.traits</x:v>
+      </x:c>
+      <x:c r="H43" s="8" t="str">
+        <x:v>collection.boss-vending.story</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
